--- a/calculations/Pomiary flux.xlsx
+++ b/calculations/Pomiary flux.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Szkola\Studia\ngss\calculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9EC358B-D427-423A-B0BA-F5270ADA4035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A643BFF-8C3F-477D-B6B8-5CA68FB81401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Czas aktywacji akcji" sheetId="2" r:id="rId1"/>
@@ -790,10 +790,10 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="10" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="12" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="2" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -11949,6 +11949,11 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="C1:T1"/>
+    <mergeCell ref="U1:AL1"/>
+    <mergeCell ref="AM1:BD1"/>
+    <mergeCell ref="BE1:BV1"/>
+    <mergeCell ref="BW1:CN1"/>
     <mergeCell ref="C2:H2"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="CI2:CN2"/>
@@ -11959,11 +11964,6 @@
     <mergeCell ref="BQ2:BV2"/>
     <mergeCell ref="O2:T2"/>
     <mergeCell ref="U2:Z2"/>
-    <mergeCell ref="C1:T1"/>
-    <mergeCell ref="U1:AL1"/>
-    <mergeCell ref="AM1:BD1"/>
-    <mergeCell ref="BE1:BV1"/>
-    <mergeCell ref="BW1:CN1"/>
     <mergeCell ref="AA2:AF2"/>
     <mergeCell ref="AG2:AL2"/>
     <mergeCell ref="AM2:AR2"/>
@@ -14341,6 +14341,16 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="H2:M2"/>
+    <mergeCell ref="N2:S2"/>
+    <mergeCell ref="T2:Y2"/>
+    <mergeCell ref="Z2:AE2"/>
+    <mergeCell ref="B1:S1"/>
+    <mergeCell ref="T1:AK1"/>
+    <mergeCell ref="AL1:BC1"/>
+    <mergeCell ref="BD1:BU1"/>
+    <mergeCell ref="BV1:CM1"/>
     <mergeCell ref="BP2:BU2"/>
     <mergeCell ref="BV2:CA2"/>
     <mergeCell ref="CB2:CG2"/>
@@ -14351,16 +14361,6 @@
     <mergeCell ref="AX2:BC2"/>
     <mergeCell ref="BD2:BI2"/>
     <mergeCell ref="BJ2:BO2"/>
-    <mergeCell ref="B1:S1"/>
-    <mergeCell ref="T1:AK1"/>
-    <mergeCell ref="AL1:BC1"/>
-    <mergeCell ref="BD1:BU1"/>
-    <mergeCell ref="BV1:CM1"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="H2:M2"/>
-    <mergeCell ref="N2:S2"/>
-    <mergeCell ref="T2:Y2"/>
-    <mergeCell ref="Z2:AE2"/>
   </mergeCells>
   <conditionalFormatting sqref="B10:CM10">
     <cfRule type="colorScale" priority="1">
@@ -15046,7 +15046,7 @@
         <v>557.67499999981305</v>
       </c>
       <c r="AE4" s="9">
-        <v>33.471927401400819</v>
+        <v>33.471927401400798</v>
       </c>
       <c r="AF4" s="11">
         <v>0.69499999992549399</v>
@@ -21609,6 +21609,14 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B1:S1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="H2:M2"/>
+    <mergeCell ref="N2:S2"/>
+    <mergeCell ref="T1:AK1"/>
+    <mergeCell ref="T2:Y2"/>
+    <mergeCell ref="Z2:AE2"/>
+    <mergeCell ref="AF2:AK2"/>
     <mergeCell ref="BV1:CM1"/>
     <mergeCell ref="BV2:CA2"/>
     <mergeCell ref="CB2:CG2"/>
@@ -21621,14 +21629,6 @@
     <mergeCell ref="BD2:BI2"/>
     <mergeCell ref="BJ2:BO2"/>
     <mergeCell ref="BP2:BU2"/>
-    <mergeCell ref="B1:S1"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="H2:M2"/>
-    <mergeCell ref="N2:S2"/>
-    <mergeCell ref="T1:AK1"/>
-    <mergeCell ref="T2:Y2"/>
-    <mergeCell ref="Z2:AE2"/>
-    <mergeCell ref="AF2:AK2"/>
   </mergeCells>
   <conditionalFormatting sqref="B23:CM23">
     <cfRule type="colorScale" priority="1">
@@ -21655,7 +21655,8 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -30399,11 +30400,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="AX3:BC3"/>
-    <mergeCell ref="BD3:BI3"/>
-    <mergeCell ref="BJ3:BO3"/>
-    <mergeCell ref="BP3:BU3"/>
-    <mergeCell ref="BV2:CM2"/>
     <mergeCell ref="AF3:AK3"/>
     <mergeCell ref="B2:S2"/>
     <mergeCell ref="T2:AK2"/>
@@ -30414,11 +30410,16 @@
     <mergeCell ref="N3:S3"/>
     <mergeCell ref="T3:Y3"/>
     <mergeCell ref="Z3:AE3"/>
+    <mergeCell ref="AL3:AQ3"/>
+    <mergeCell ref="AR3:AW3"/>
+    <mergeCell ref="AX3:BC3"/>
+    <mergeCell ref="BD3:BI3"/>
+    <mergeCell ref="BJ3:BO3"/>
+    <mergeCell ref="BP3:BU3"/>
+    <mergeCell ref="BV2:CM2"/>
     <mergeCell ref="BV3:CA3"/>
     <mergeCell ref="CB3:CG3"/>
     <mergeCell ref="CH3:CM3"/>
-    <mergeCell ref="AL3:AQ3"/>
-    <mergeCell ref="AR3:AW3"/>
   </mergeCells>
   <conditionalFormatting sqref="B25:CM25">
     <cfRule type="colorScale" priority="2">
@@ -30445,6 +30446,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -30498,10 +30500,10 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="34" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="9" t="s">
@@ -30530,8 +30532,8 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A3" s="35"/>
-      <c r="B3" s="35"/>
+      <c r="A3" s="34"/>
+      <c r="B3" s="34"/>
       <c r="C3" s="9" t="s">
         <v>10</v>
       </c>
@@ -30558,8 +30560,8 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A4" s="35"/>
-      <c r="B4" s="35"/>
+      <c r="A4" s="34"/>
+      <c r="B4" s="34"/>
       <c r="C4" s="9" t="s">
         <v>13</v>
       </c>
@@ -30586,8 +30588,8 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A5" s="35"/>
-      <c r="B5" s="35"/>
+      <c r="A5" s="34"/>
+      <c r="B5" s="34"/>
       <c r="C5" s="9" t="s">
         <v>9</v>
       </c>
@@ -30614,8 +30616,8 @@
       </c>
     </row>
     <row r="6" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A6" s="35"/>
-      <c r="B6" s="35"/>
+      <c r="A6" s="34"/>
+      <c r="B6" s="34"/>
       <c r="C6" s="9" t="s">
         <v>12</v>
       </c>
@@ -30642,8 +30644,8 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A7" s="35"/>
-      <c r="B7" s="35"/>
+      <c r="A7" s="34"/>
+      <c r="B7" s="34"/>
       <c r="C7" s="9" t="s">
         <v>8</v>
       </c>
@@ -30670,8 +30672,8 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A8" s="35"/>
-      <c r="B8" s="34" t="s">
+      <c r="A8" s="34"/>
+      <c r="B8" s="35" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="11" t="s">
@@ -30700,8 +30702,8 @@
       </c>
     </row>
     <row r="9" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A9" s="35"/>
-      <c r="B9" s="34"/>
+      <c r="A9" s="34"/>
+      <c r="B9" s="35"/>
       <c r="C9" s="11" t="s">
         <v>10</v>
       </c>
@@ -30728,8 +30730,8 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A10" s="35"/>
-      <c r="B10" s="34"/>
+      <c r="A10" s="34"/>
+      <c r="B10" s="35"/>
       <c r="C10" s="11" t="s">
         <v>13</v>
       </c>
@@ -30756,8 +30758,8 @@
       </c>
     </row>
     <row r="11" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A11" s="35"/>
-      <c r="B11" s="34"/>
+      <c r="A11" s="34"/>
+      <c r="B11" s="35"/>
       <c r="C11" s="11" t="s">
         <v>9</v>
       </c>
@@ -30784,8 +30786,8 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A12" s="35"/>
-      <c r="B12" s="34"/>
+      <c r="A12" s="34"/>
+      <c r="B12" s="35"/>
       <c r="C12" s="11" t="s">
         <v>12</v>
       </c>
@@ -30812,8 +30814,8 @@
       </c>
     </row>
     <row r="13" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A13" s="35"/>
-      <c r="B13" s="34"/>
+      <c r="A13" s="34"/>
+      <c r="B13" s="35"/>
       <c r="C13" s="11" t="s">
         <v>8</v>
       </c>
@@ -30840,8 +30842,8 @@
       </c>
     </row>
     <row r="14" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A14" s="35"/>
-      <c r="B14" s="35" t="s">
+      <c r="A14" s="34"/>
+      <c r="B14" s="34" t="s">
         <v>6</v>
       </c>
       <c r="C14" s="9" t="s">
@@ -30870,8 +30872,8 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A15" s="35"/>
-      <c r="B15" s="35"/>
+      <c r="A15" s="34"/>
+      <c r="B15" s="34"/>
       <c r="C15" s="9" t="s">
         <v>10</v>
       </c>
@@ -30898,8 +30900,8 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A16" s="35"/>
-      <c r="B16" s="35"/>
+      <c r="A16" s="34"/>
+      <c r="B16" s="34"/>
       <c r="C16" s="9" t="s">
         <v>13</v>
       </c>
@@ -30926,8 +30928,8 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A17" s="35"/>
-      <c r="B17" s="35"/>
+      <c r="A17" s="34"/>
+      <c r="B17" s="34"/>
       <c r="C17" s="9" t="s">
         <v>9</v>
       </c>
@@ -30954,8 +30956,8 @@
       </c>
     </row>
     <row r="18" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A18" s="35"/>
-      <c r="B18" s="35"/>
+      <c r="A18" s="34"/>
+      <c r="B18" s="34"/>
       <c r="C18" s="9" t="s">
         <v>12</v>
       </c>
@@ -30982,8 +30984,8 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A19" s="35"/>
-      <c r="B19" s="35"/>
+      <c r="A19" s="34"/>
+      <c r="B19" s="34"/>
       <c r="C19" s="9" t="s">
         <v>8</v>
       </c>
@@ -31010,10 +31012,10 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="15.75" thickTop="1">
-      <c r="A20" s="34" t="s">
+      <c r="A20" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="34" t="s">
+      <c r="B20" s="35" t="s">
         <v>5</v>
       </c>
       <c r="C20" s="11" t="s">
@@ -31042,8 +31044,8 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="34"/>
-      <c r="B21" s="34"/>
+      <c r="A21" s="35"/>
+      <c r="B21" s="35"/>
       <c r="C21" s="11" t="s">
         <v>10</v>
       </c>
@@ -31070,8 +31072,8 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="34"/>
-      <c r="B22" s="34"/>
+      <c r="A22" s="35"/>
+      <c r="B22" s="35"/>
       <c r="C22" s="11" t="s">
         <v>13</v>
       </c>
@@ -31098,8 +31100,8 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="15">
-      <c r="A23" s="34"/>
-      <c r="B23" s="34"/>
+      <c r="A23" s="35"/>
+      <c r="B23" s="35"/>
       <c r="C23" s="11" t="s">
         <v>9</v>
       </c>
@@ -31126,8 +31128,8 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="15">
-      <c r="A24" s="34"/>
-      <c r="B24" s="34"/>
+      <c r="A24" s="35"/>
+      <c r="B24" s="35"/>
       <c r="C24" s="11" t="s">
         <v>12</v>
       </c>
@@ -31154,8 +31156,8 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A25" s="34"/>
-      <c r="B25" s="34"/>
+      <c r="A25" s="35"/>
+      <c r="B25" s="35"/>
       <c r="C25" s="11" t="s">
         <v>8</v>
       </c>
@@ -31182,8 +31184,8 @@
       </c>
     </row>
     <row r="26" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A26" s="34"/>
-      <c r="B26" s="35" t="s">
+      <c r="A26" s="35"/>
+      <c r="B26" s="34" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="9" t="s">
@@ -31212,8 +31214,8 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A27" s="34"/>
-      <c r="B27" s="35"/>
+      <c r="A27" s="35"/>
+      <c r="B27" s="34"/>
       <c r="C27" s="9" t="s">
         <v>10</v>
       </c>
@@ -31240,8 +31242,8 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A28" s="34"/>
-      <c r="B28" s="35"/>
+      <c r="A28" s="35"/>
+      <c r="B28" s="34"/>
       <c r="C28" s="9" t="s">
         <v>13</v>
       </c>
@@ -31268,8 +31270,8 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A29" s="34"/>
-      <c r="B29" s="35"/>
+      <c r="A29" s="35"/>
+      <c r="B29" s="34"/>
       <c r="C29" s="9" t="s">
         <v>9</v>
       </c>
@@ -31296,8 +31298,8 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A30" s="34"/>
-      <c r="B30" s="35"/>
+      <c r="A30" s="35"/>
+      <c r="B30" s="34"/>
       <c r="C30" s="9" t="s">
         <v>12</v>
       </c>
@@ -31324,8 +31326,8 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A31" s="34"/>
-      <c r="B31" s="35"/>
+      <c r="A31" s="35"/>
+      <c r="B31" s="34"/>
       <c r="C31" s="9" t="s">
         <v>8</v>
       </c>
@@ -31352,8 +31354,8 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="15.75" thickTop="1">
-      <c r="A32" s="34"/>
-      <c r="B32" s="34" t="s">
+      <c r="A32" s="35"/>
+      <c r="B32" s="35" t="s">
         <v>6</v>
       </c>
       <c r="C32" s="11" t="s">
@@ -31382,8 +31384,8 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="15">
-      <c r="A33" s="34"/>
-      <c r="B33" s="34"/>
+      <c r="A33" s="35"/>
+      <c r="B33" s="35"/>
       <c r="C33" s="11" t="s">
         <v>10</v>
       </c>
@@ -31410,8 +31412,8 @@
       </c>
     </row>
     <row r="34" spans="1:10" ht="15">
-      <c r="A34" s="34"/>
-      <c r="B34" s="34"/>
+      <c r="A34" s="35"/>
+      <c r="B34" s="35"/>
       <c r="C34" s="11" t="s">
         <v>13</v>
       </c>
@@ -31438,8 +31440,8 @@
       </c>
     </row>
     <row r="35" spans="1:10" ht="15">
-      <c r="A35" s="34"/>
-      <c r="B35" s="34"/>
+      <c r="A35" s="35"/>
+      <c r="B35" s="35"/>
       <c r="C35" s="11" t="s">
         <v>9</v>
       </c>
@@ -31466,8 +31468,8 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="15">
-      <c r="A36" s="34"/>
-      <c r="B36" s="34"/>
+      <c r="A36" s="35"/>
+      <c r="B36" s="35"/>
       <c r="C36" s="11" t="s">
         <v>12</v>
       </c>
@@ -31494,8 +31496,8 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A37" s="34"/>
-      <c r="B37" s="34"/>
+      <c r="A37" s="35"/>
+      <c r="B37" s="35"/>
       <c r="C37" s="11" t="s">
         <v>8</v>
       </c>
@@ -31522,10 +31524,10 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A38" s="35" t="s">
+      <c r="A38" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B38" s="35" t="s">
+      <c r="B38" s="34" t="s">
         <v>5</v>
       </c>
       <c r="C38" s="9" t="s">
@@ -31554,8 +31556,8 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A39" s="35"/>
-      <c r="B39" s="35"/>
+      <c r="A39" s="34"/>
+      <c r="B39" s="34"/>
       <c r="C39" s="9" t="s">
         <v>10</v>
       </c>
@@ -31582,8 +31584,8 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A40" s="35"/>
-      <c r="B40" s="35"/>
+      <c r="A40" s="34"/>
+      <c r="B40" s="34"/>
       <c r="C40" s="9" t="s">
         <v>13</v>
       </c>
@@ -31610,8 +31612,8 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A41" s="35"/>
-      <c r="B41" s="35"/>
+      <c r="A41" s="34"/>
+      <c r="B41" s="34"/>
       <c r="C41" s="9" t="s">
         <v>9</v>
       </c>
@@ -31638,8 +31640,8 @@
       </c>
     </row>
     <row r="42" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A42" s="35"/>
-      <c r="B42" s="35"/>
+      <c r="A42" s="34"/>
+      <c r="B42" s="34"/>
       <c r="C42" s="9" t="s">
         <v>12</v>
       </c>
@@ -31666,8 +31668,8 @@
       </c>
     </row>
     <row r="43" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A43" s="35"/>
-      <c r="B43" s="35"/>
+      <c r="A43" s="34"/>
+      <c r="B43" s="34"/>
       <c r="C43" s="9" t="s">
         <v>8</v>
       </c>
@@ -31694,8 +31696,8 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A44" s="35"/>
-      <c r="B44" s="34" t="s">
+      <c r="A44" s="34"/>
+      <c r="B44" s="35" t="s">
         <v>7</v>
       </c>
       <c r="C44" s="11" t="s">
@@ -31724,8 +31726,8 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A45" s="35"/>
-      <c r="B45" s="34"/>
+      <c r="A45" s="34"/>
+      <c r="B45" s="35"/>
       <c r="C45" s="11" t="s">
         <v>10</v>
       </c>
@@ -31752,8 +31754,8 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A46" s="35"/>
-      <c r="B46" s="34"/>
+      <c r="A46" s="34"/>
+      <c r="B46" s="35"/>
       <c r="C46" s="11" t="s">
         <v>13</v>
       </c>
@@ -31780,8 +31782,8 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A47" s="35"/>
-      <c r="B47" s="34"/>
+      <c r="A47" s="34"/>
+      <c r="B47" s="35"/>
       <c r="C47" s="11" t="s">
         <v>9</v>
       </c>
@@ -31808,8 +31810,8 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A48" s="35"/>
-      <c r="B48" s="34"/>
+      <c r="A48" s="34"/>
+      <c r="B48" s="35"/>
       <c r="C48" s="11" t="s">
         <v>12</v>
       </c>
@@ -31836,8 +31838,8 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A49" s="35"/>
-      <c r="B49" s="34"/>
+      <c r="A49" s="34"/>
+      <c r="B49" s="35"/>
       <c r="C49" s="11" t="s">
         <v>8</v>
       </c>
@@ -31864,8 +31866,8 @@
       </c>
     </row>
     <row r="50" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A50" s="35"/>
-      <c r="B50" s="35" t="s">
+      <c r="A50" s="34"/>
+      <c r="B50" s="34" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="9" t="s">
@@ -31894,8 +31896,8 @@
       </c>
     </row>
     <row r="51" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A51" s="35"/>
-      <c r="B51" s="35"/>
+      <c r="A51" s="34"/>
+      <c r="B51" s="34"/>
       <c r="C51" s="9" t="s">
         <v>10</v>
       </c>
@@ -31922,8 +31924,8 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A52" s="35"/>
-      <c r="B52" s="35"/>
+      <c r="A52" s="34"/>
+      <c r="B52" s="34"/>
       <c r="C52" s="9" t="s">
         <v>13</v>
       </c>
@@ -31950,8 +31952,8 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A53" s="35"/>
-      <c r="B53" s="35"/>
+      <c r="A53" s="34"/>
+      <c r="B53" s="34"/>
       <c r="C53" s="9" t="s">
         <v>9</v>
       </c>
@@ -31978,8 +31980,8 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A54" s="35"/>
-      <c r="B54" s="35"/>
+      <c r="A54" s="34"/>
+      <c r="B54" s="34"/>
       <c r="C54" s="9" t="s">
         <v>12</v>
       </c>
@@ -32006,8 +32008,8 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A55" s="35"/>
-      <c r="B55" s="35"/>
+      <c r="A55" s="34"/>
+      <c r="B55" s="34"/>
       <c r="C55" s="9" t="s">
         <v>8</v>
       </c>
@@ -32034,10 +32036,10 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="15.75" thickTop="1">
-      <c r="A56" s="34" t="s">
+      <c r="A56" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="B56" s="34" t="s">
+      <c r="B56" s="35" t="s">
         <v>5</v>
       </c>
       <c r="C56" s="11" t="s">
@@ -32066,8 +32068,8 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="15">
-      <c r="A57" s="34"/>
-      <c r="B57" s="34"/>
+      <c r="A57" s="35"/>
+      <c r="B57" s="35"/>
       <c r="C57" s="11" t="s">
         <v>10</v>
       </c>
@@ -32094,8 +32096,8 @@
       </c>
     </row>
     <row r="58" spans="1:10" ht="15">
-      <c r="A58" s="34"/>
-      <c r="B58" s="34"/>
+      <c r="A58" s="35"/>
+      <c r="B58" s="35"/>
       <c r="C58" s="11" t="s">
         <v>13</v>
       </c>
@@ -32122,8 +32124,8 @@
       </c>
     </row>
     <row r="59" spans="1:10" ht="15">
-      <c r="A59" s="34"/>
-      <c r="B59" s="34"/>
+      <c r="A59" s="35"/>
+      <c r="B59" s="35"/>
       <c r="C59" s="11" t="s">
         <v>9</v>
       </c>
@@ -32150,8 +32152,8 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="15">
-      <c r="A60" s="34"/>
-      <c r="B60" s="34"/>
+      <c r="A60" s="35"/>
+      <c r="B60" s="35"/>
       <c r="C60" s="11" t="s">
         <v>12</v>
       </c>
@@ -32178,8 +32180,8 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A61" s="34"/>
-      <c r="B61" s="34"/>
+      <c r="A61" s="35"/>
+      <c r="B61" s="35"/>
       <c r="C61" s="11" t="s">
         <v>8</v>
       </c>
@@ -32206,8 +32208,8 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A62" s="34"/>
-      <c r="B62" s="35" t="s">
+      <c r="A62" s="35"/>
+      <c r="B62" s="34" t="s">
         <v>7</v>
       </c>
       <c r="C62" s="9" t="s">
@@ -32236,8 +32238,8 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A63" s="34"/>
-      <c r="B63" s="35"/>
+      <c r="A63" s="35"/>
+      <c r="B63" s="34"/>
       <c r="C63" s="9" t="s">
         <v>10</v>
       </c>
@@ -32264,8 +32266,8 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A64" s="34"/>
-      <c r="B64" s="35"/>
+      <c r="A64" s="35"/>
+      <c r="B64" s="34"/>
       <c r="C64" s="9" t="s">
         <v>13</v>
       </c>
@@ -32292,8 +32294,8 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A65" s="34"/>
-      <c r="B65" s="35"/>
+      <c r="A65" s="35"/>
+      <c r="B65" s="34"/>
       <c r="C65" s="9" t="s">
         <v>9</v>
       </c>
@@ -32320,8 +32322,8 @@
       </c>
     </row>
     <row r="66" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A66" s="34"/>
-      <c r="B66" s="35"/>
+      <c r="A66" s="35"/>
+      <c r="B66" s="34"/>
       <c r="C66" s="9" t="s">
         <v>12</v>
       </c>
@@ -32348,8 +32350,8 @@
       </c>
     </row>
     <row r="67" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A67" s="34"/>
-      <c r="B67" s="35"/>
+      <c r="A67" s="35"/>
+      <c r="B67" s="34"/>
       <c r="C67" s="9" t="s">
         <v>8</v>
       </c>
@@ -32376,8 +32378,8 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="15.75" thickTop="1">
-      <c r="A68" s="34"/>
-      <c r="B68" s="34" t="s">
+      <c r="A68" s="35"/>
+      <c r="B68" s="35" t="s">
         <v>6</v>
       </c>
       <c r="C68" s="11" t="s">
@@ -32406,8 +32408,8 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="15">
-      <c r="A69" s="34"/>
-      <c r="B69" s="34"/>
+      <c r="A69" s="35"/>
+      <c r="B69" s="35"/>
       <c r="C69" s="11" t="s">
         <v>10</v>
       </c>
@@ -32434,8 +32436,8 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="15">
-      <c r="A70" s="34"/>
-      <c r="B70" s="34"/>
+      <c r="A70" s="35"/>
+      <c r="B70" s="35"/>
       <c r="C70" s="11" t="s">
         <v>13</v>
       </c>
@@ -32462,8 +32464,8 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="15">
-      <c r="A71" s="34"/>
-      <c r="B71" s="34"/>
+      <c r="A71" s="35"/>
+      <c r="B71" s="35"/>
       <c r="C71" s="11" t="s">
         <v>9</v>
       </c>
@@ -32490,8 +32492,8 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="15">
-      <c r="A72" s="34"/>
-      <c r="B72" s="34"/>
+      <c r="A72" s="35"/>
+      <c r="B72" s="35"/>
       <c r="C72" s="11" t="s">
         <v>12</v>
       </c>
@@ -32518,8 +32520,8 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A73" s="34"/>
-      <c r="B73" s="34"/>
+      <c r="A73" s="35"/>
+      <c r="B73" s="35"/>
       <c r="C73" s="11" t="s">
         <v>8</v>
       </c>
@@ -32546,10 +32548,10 @@
       </c>
     </row>
     <row r="74" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A74" s="35" t="s">
+      <c r="A74" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="B74" s="35" t="s">
+      <c r="B74" s="34" t="s">
         <v>5</v>
       </c>
       <c r="C74" s="9" t="s">
@@ -32578,8 +32580,8 @@
       </c>
     </row>
     <row r="75" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A75" s="35"/>
-      <c r="B75" s="35"/>
+      <c r="A75" s="34"/>
+      <c r="B75" s="34"/>
       <c r="C75" s="9" t="s">
         <v>10</v>
       </c>
@@ -32606,8 +32608,8 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A76" s="35"/>
-      <c r="B76" s="35"/>
+      <c r="A76" s="34"/>
+      <c r="B76" s="34"/>
       <c r="C76" s="9" t="s">
         <v>13</v>
       </c>
@@ -32634,8 +32636,8 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A77" s="35"/>
-      <c r="B77" s="35"/>
+      <c r="A77" s="34"/>
+      <c r="B77" s="34"/>
       <c r="C77" s="9" t="s">
         <v>9</v>
       </c>
@@ -32662,8 +32664,8 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A78" s="35"/>
-      <c r="B78" s="35"/>
+      <c r="A78" s="34"/>
+      <c r="B78" s="34"/>
       <c r="C78" s="9" t="s">
         <v>12</v>
       </c>
@@ -32690,8 +32692,8 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A79" s="35"/>
-      <c r="B79" s="35"/>
+      <c r="A79" s="34"/>
+      <c r="B79" s="34"/>
       <c r="C79" s="9" t="s">
         <v>8</v>
       </c>
@@ -32718,8 +32720,8 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A80" s="35"/>
-      <c r="B80" s="34" t="s">
+      <c r="A80" s="34"/>
+      <c r="B80" s="35" t="s">
         <v>7</v>
       </c>
       <c r="C80" s="11" t="s">
@@ -32748,8 +32750,8 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A81" s="35"/>
-      <c r="B81" s="34"/>
+      <c r="A81" s="34"/>
+      <c r="B81" s="35"/>
       <c r="C81" s="11" t="s">
         <v>10</v>
       </c>
@@ -32776,8 +32778,8 @@
       </c>
     </row>
     <row r="82" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A82" s="35"/>
-      <c r="B82" s="34"/>
+      <c r="A82" s="34"/>
+      <c r="B82" s="35"/>
       <c r="C82" s="11" t="s">
         <v>13</v>
       </c>
@@ -32804,8 +32806,8 @@
       </c>
     </row>
     <row r="83" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A83" s="35"/>
-      <c r="B83" s="34"/>
+      <c r="A83" s="34"/>
+      <c r="B83" s="35"/>
       <c r="C83" s="11" t="s">
         <v>9</v>
       </c>
@@ -32832,8 +32834,8 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A84" s="35"/>
-      <c r="B84" s="34"/>
+      <c r="A84" s="34"/>
+      <c r="B84" s="35"/>
       <c r="C84" s="11" t="s">
         <v>12</v>
       </c>
@@ -32860,8 +32862,8 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A85" s="35"/>
-      <c r="B85" s="34"/>
+      <c r="A85" s="34"/>
+      <c r="B85" s="35"/>
       <c r="C85" s="11" t="s">
         <v>8</v>
       </c>
@@ -32888,8 +32890,8 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A86" s="35"/>
-      <c r="B86" s="35" t="s">
+      <c r="A86" s="34"/>
+      <c r="B86" s="34" t="s">
         <v>6</v>
       </c>
       <c r="C86" s="9" t="s">
@@ -32918,8 +32920,8 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A87" s="35"/>
-      <c r="B87" s="35"/>
+      <c r="A87" s="34"/>
+      <c r="B87" s="34"/>
       <c r="C87" s="9" t="s">
         <v>10</v>
       </c>
@@ -32946,8 +32948,8 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A88" s="35"/>
-      <c r="B88" s="35"/>
+      <c r="A88" s="34"/>
+      <c r="B88" s="34"/>
       <c r="C88" s="9" t="s">
         <v>13</v>
       </c>
@@ -32974,8 +32976,8 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A89" s="35"/>
-      <c r="B89" s="35"/>
+      <c r="A89" s="34"/>
+      <c r="B89" s="34"/>
       <c r="C89" s="9" t="s">
         <v>9</v>
       </c>
@@ -33002,8 +33004,8 @@
       </c>
     </row>
     <row r="90" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A90" s="35"/>
-      <c r="B90" s="35"/>
+      <c r="A90" s="34"/>
+      <c r="B90" s="34"/>
       <c r="C90" s="9" t="s">
         <v>12</v>
       </c>
@@ -33030,8 +33032,8 @@
       </c>
     </row>
     <row r="91" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A91" s="35"/>
-      <c r="B91" s="35"/>
+      <c r="A91" s="34"/>
+      <c r="B91" s="34"/>
       <c r="C91" s="9" t="s">
         <v>8</v>
       </c>
@@ -33060,6 +33062,10 @@
     <row r="92" spans="1:10" ht="13.5" thickTop="1"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B74:B79"/>
+    <mergeCell ref="B80:B85"/>
+    <mergeCell ref="B86:B91"/>
+    <mergeCell ref="A74:A91"/>
     <mergeCell ref="A2:A19"/>
     <mergeCell ref="A20:A37"/>
     <mergeCell ref="A38:A55"/>
@@ -33076,10 +33082,6 @@
     <mergeCell ref="B20:B25"/>
     <mergeCell ref="B56:B61"/>
     <mergeCell ref="B68:B73"/>
-    <mergeCell ref="B74:B79"/>
-    <mergeCell ref="B80:B85"/>
-    <mergeCell ref="B86:B91"/>
-    <mergeCell ref="A74:A91"/>
   </mergeCells>
   <conditionalFormatting sqref="D2:D91">
     <cfRule type="colorScale" priority="6">
@@ -33129,18 +33131,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J91">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="H2:H91">
     <cfRule type="colorScale" priority="2">
       <colorScale>
@@ -33165,6 +33155,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J91">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>